--- a/artfynd/A 29455-2024 artfynd.xlsx
+++ b/artfynd/A 29455-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121345126</v>
+        <v>121345841</v>
       </c>
       <c r="B3" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518549</v>
+        <v>518331</v>
       </c>
       <c r="R3" t="n">
-        <v>6994945</v>
+        <v>6995058</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121345492</v>
+        <v>121346453</v>
       </c>
       <c r="B4" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,17 +948,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518419</v>
+        <v>518587</v>
       </c>
       <c r="R4" t="n">
-        <v>6994943</v>
+        <v>6994869</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121346471</v>
+        <v>121345790</v>
       </c>
       <c r="B5" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,14 +1060,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518606</v>
+        <v>518340</v>
       </c>
       <c r="R5" t="n">
-        <v>6994830</v>
+        <v>6995031</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121345841</v>
+        <v>121345245</v>
       </c>
       <c r="B6" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,17 +1172,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518331</v>
+        <v>518511</v>
       </c>
       <c r="R6" t="n">
-        <v>6995058</v>
+        <v>6994904</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121345682</v>
+        <v>121345292</v>
       </c>
       <c r="B7" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,17 +1284,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518350</v>
+        <v>518458</v>
       </c>
       <c r="R7" t="n">
-        <v>6995000</v>
+        <v>6994899</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121345292</v>
+        <v>121345182</v>
       </c>
       <c r="B8" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1396,14 +1396,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518458</v>
+        <v>518545</v>
       </c>
       <c r="R8" t="n">
-        <v>6994899</v>
+        <v>6994921</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121345258</v>
+        <v>121345279</v>
       </c>
       <c r="B9" t="n">
-        <v>90687</v>
+        <v>78601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1488,21 +1488,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518502</v>
+        <v>518470</v>
       </c>
       <c r="R9" t="n">
-        <v>6994901</v>
+        <v>6994910</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121345245</v>
+        <v>121345407</v>
       </c>
       <c r="B10" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518511</v>
+        <v>518425</v>
       </c>
       <c r="R10" t="n">
-        <v>6994904</v>
+        <v>6994937</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121346453</v>
+        <v>121345258</v>
       </c>
       <c r="B11" t="n">
-        <v>78598</v>
+        <v>90697</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,34 +1712,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518587</v>
+        <v>518502</v>
       </c>
       <c r="R11" t="n">
-        <v>6994869</v>
+        <v>6994901</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121345795</v>
+        <v>121345126</v>
       </c>
       <c r="B12" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1824,34 +1824,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518338</v>
+        <v>518549</v>
       </c>
       <c r="R12" t="n">
-        <v>6995040</v>
+        <v>6994945</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,7 +1923,7 @@
         <v>121345798</v>
       </c>
       <c r="B13" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>121345815</v>
       </c>
       <c r="B14" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121345182</v>
+        <v>121345795</v>
       </c>
       <c r="B15" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2160,34 +2160,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518545</v>
+        <v>518338</v>
       </c>
       <c r="R15" t="n">
-        <v>6994921</v>
+        <v>6995040</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,10 +2256,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121345279</v>
+        <v>121345682</v>
       </c>
       <c r="B16" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2292,17 +2292,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518470</v>
+        <v>518350</v>
       </c>
       <c r="R16" t="n">
-        <v>6994910</v>
+        <v>6995000</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,10 +2368,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121345407</v>
+        <v>121346471</v>
       </c>
       <c r="B17" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2404,14 +2404,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518425</v>
+        <v>518606</v>
       </c>
       <c r="R17" t="n">
-        <v>6994937</v>
+        <v>6994830</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,10 +2480,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121345790</v>
+        <v>121345492</v>
       </c>
       <c r="B18" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2516,17 +2516,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518340</v>
+        <v>518419</v>
       </c>
       <c r="R18" t="n">
-        <v>6995031</v>
+        <v>6994943</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 29455-2024 artfynd.xlsx
+++ b/artfynd/A 29455-2024 artfynd.xlsx
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121345841</v>
+        <v>121346453</v>
       </c>
       <c r="B3" t="n">
         <v>78601</v>
@@ -836,17 +836,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518331</v>
+        <v>518587</v>
       </c>
       <c r="R3" t="n">
-        <v>6995058</v>
+        <v>6994869</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +912,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121346453</v>
+        <v>121345790</v>
       </c>
       <c r="B4" t="n">
         <v>78601</v>
@@ -948,14 +948,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518587</v>
+        <v>518340</v>
       </c>
       <c r="R4" t="n">
-        <v>6994869</v>
+        <v>6995031</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121345790</v>
+        <v>121345841</v>
       </c>
       <c r="B5" t="n">
         <v>78601</v>
@@ -1064,13 +1064,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518340</v>
+        <v>518331</v>
       </c>
       <c r="R5" t="n">
-        <v>6995031</v>
+        <v>6995058</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 29455-2024 artfynd.xlsx
+++ b/artfynd/A 29455-2024 artfynd.xlsx
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121346453</v>
+        <v>121345841</v>
       </c>
       <c r="B3" t="n">
         <v>78601</v>
@@ -836,17 +836,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518587</v>
+        <v>518331</v>
       </c>
       <c r="R3" t="n">
-        <v>6994869</v>
+        <v>6995058</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121345790</v>
+        <v>121345258</v>
       </c>
       <c r="B4" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,34 +928,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518340</v>
+        <v>518502</v>
       </c>
       <c r="R4" t="n">
-        <v>6995031</v>
+        <v>6994901</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121345841</v>
+        <v>121345492</v>
       </c>
       <c r="B5" t="n">
         <v>78601</v>
@@ -1060,17 +1060,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518331</v>
+        <v>518419</v>
       </c>
       <c r="R5" t="n">
-        <v>6995058</v>
+        <v>6994943</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,7 +1136,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121345245</v>
+        <v>121346471</v>
       </c>
       <c r="B6" t="n">
         <v>78601</v>
@@ -1172,17 +1172,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518511</v>
+        <v>518606</v>
       </c>
       <c r="R6" t="n">
-        <v>6994904</v>
+        <v>6994830</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1360,7 +1360,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121345182</v>
+        <v>121345790</v>
       </c>
       <c r="B8" t="n">
         <v>78601</v>
@@ -1396,14 +1396,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518545</v>
+        <v>518340</v>
       </c>
       <c r="R8" t="n">
-        <v>6994921</v>
+        <v>6995031</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,7 +1472,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121345279</v>
+        <v>121345245</v>
       </c>
       <c r="B9" t="n">
         <v>78601</v>
@@ -1512,13 +1512,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518470</v>
+        <v>518511</v>
       </c>
       <c r="R9" t="n">
-        <v>6994910</v>
+        <v>6994904</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,7 +1584,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121345407</v>
+        <v>121345682</v>
       </c>
       <c r="B10" t="n">
         <v>78601</v>
@@ -1620,17 +1620,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518425</v>
+        <v>518350</v>
       </c>
       <c r="R10" t="n">
-        <v>6994937</v>
+        <v>6995000</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121345258</v>
+        <v>121345798</v>
       </c>
       <c r="B11" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,37 +1712,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518502</v>
+        <v>518332</v>
       </c>
       <c r="R11" t="n">
-        <v>6994901</v>
+        <v>6995045</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121345126</v>
+        <v>121345815</v>
       </c>
       <c r="B12" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1824,34 +1824,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518549</v>
+        <v>518330</v>
       </c>
       <c r="R12" t="n">
-        <v>6994945</v>
+        <v>6995067</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,7 +1920,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121345798</v>
+        <v>121345279</v>
       </c>
       <c r="B13" t="n">
         <v>78601</v>
@@ -1956,17 +1956,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518332</v>
+        <v>518470</v>
       </c>
       <c r="R13" t="n">
-        <v>6995045</v>
+        <v>6994910</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,7 +2032,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121345815</v>
+        <v>121345795</v>
       </c>
       <c r="B14" t="n">
         <v>79682</v>
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518330</v>
+        <v>518338</v>
       </c>
       <c r="R14" t="n">
-        <v>6995067</v>
+        <v>6995040</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,10 +2144,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121345795</v>
+        <v>121346453</v>
       </c>
       <c r="B15" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2160,34 +2160,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518338</v>
+        <v>518587</v>
       </c>
       <c r="R15" t="n">
-        <v>6995040</v>
+        <v>6994869</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,7 +2256,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121345682</v>
+        <v>121345182</v>
       </c>
       <c r="B16" t="n">
         <v>78601</v>
@@ -2292,17 +2292,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518350</v>
+        <v>518545</v>
       </c>
       <c r="R16" t="n">
-        <v>6995000</v>
+        <v>6994921</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,7 +2368,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121346471</v>
+        <v>121345126</v>
       </c>
       <c r="B17" t="n">
         <v>78601</v>
@@ -2404,14 +2404,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518606</v>
+        <v>518549</v>
       </c>
       <c r="R17" t="n">
-        <v>6994830</v>
+        <v>6994945</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,7 +2480,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121345492</v>
+        <v>121345407</v>
       </c>
       <c r="B18" t="n">
         <v>78601</v>
@@ -2520,13 +2520,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518419</v>
+        <v>518425</v>
       </c>
       <c r="R18" t="n">
-        <v>6994943</v>
+        <v>6994937</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 29455-2024 artfynd.xlsx
+++ b/artfynd/A 29455-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121345841</v>
+        <v>121345258</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,37 +816,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518331</v>
+        <v>518502</v>
       </c>
       <c r="R3" t="n">
-        <v>6995058</v>
+        <v>6994901</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121345258</v>
+        <v>121345841</v>
       </c>
       <c r="B4" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,37 +928,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518502</v>
+        <v>518331</v>
       </c>
       <c r="R4" t="n">
-        <v>6994901</v>
+        <v>6995058</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 29455-2024 artfynd.xlsx
+++ b/artfynd/A 29455-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121345258</v>
+        <v>121345815</v>
       </c>
       <c r="B3" t="n">
-        <v>90697</v>
+        <v>79685</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,34 +816,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518502</v>
+        <v>518330</v>
       </c>
       <c r="R3" t="n">
-        <v>6994901</v>
+        <v>6995067</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121345841</v>
+        <v>121345682</v>
       </c>
       <c r="B4" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,13 +952,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518331</v>
+        <v>518350</v>
       </c>
       <c r="R4" t="n">
-        <v>6995058</v>
+        <v>6995000</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121345492</v>
+        <v>121345126</v>
       </c>
       <c r="B5" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,17 +1060,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518419</v>
+        <v>518549</v>
       </c>
       <c r="R5" t="n">
-        <v>6994943</v>
+        <v>6994945</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121346471</v>
+        <v>121345292</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,14 +1172,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518606</v>
+        <v>518458</v>
       </c>
       <c r="R6" t="n">
-        <v>6994830</v>
+        <v>6994899</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121345292</v>
+        <v>121345279</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518458</v>
+        <v>518470</v>
       </c>
       <c r="R7" t="n">
-        <v>6994899</v>
+        <v>6994910</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121345790</v>
+        <v>121345798</v>
       </c>
       <c r="B8" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518340</v>
+        <v>518332</v>
       </c>
       <c r="R8" t="n">
-        <v>6995031</v>
+        <v>6995045</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121345245</v>
+        <v>121345795</v>
       </c>
       <c r="B9" t="n">
-        <v>78601</v>
+        <v>79685</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1488,37 +1488,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518511</v>
+        <v>518338</v>
       </c>
       <c r="R9" t="n">
-        <v>6994904</v>
+        <v>6995040</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121345682</v>
+        <v>121345245</v>
       </c>
       <c r="B10" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,14 +1620,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518350</v>
+        <v>518511</v>
       </c>
       <c r="R10" t="n">
-        <v>6995000</v>
+        <v>6994904</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121345798</v>
+        <v>121345841</v>
       </c>
       <c r="B11" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518332</v>
+        <v>518331</v>
       </c>
       <c r="R11" t="n">
-        <v>6995045</v>
+        <v>6995058</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121345815</v>
+        <v>121345492</v>
       </c>
       <c r="B12" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1824,37 +1824,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518330</v>
+        <v>518419</v>
       </c>
       <c r="R12" t="n">
-        <v>6995067</v>
+        <v>6994943</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,10 +1920,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121345279</v>
+        <v>121345407</v>
       </c>
       <c r="B13" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518470</v>
+        <v>518425</v>
       </c>
       <c r="R13" t="n">
-        <v>6994910</v>
+        <v>6994937</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,10 +2032,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121345795</v>
+        <v>121345790</v>
       </c>
       <c r="B14" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2048,21 +2048,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518338</v>
+        <v>518340</v>
       </c>
       <c r="R14" t="n">
-        <v>6995040</v>
+        <v>6995031</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,10 +2144,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121346453</v>
+        <v>121346471</v>
       </c>
       <c r="B15" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2180,14 +2180,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518587</v>
+        <v>518606</v>
       </c>
       <c r="R15" t="n">
-        <v>6994869</v>
+        <v>6994830</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,10 +2256,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121345182</v>
+        <v>121345258</v>
       </c>
       <c r="B16" t="n">
-        <v>78601</v>
+        <v>90709</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2272,34 +2272,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518545</v>
+        <v>518502</v>
       </c>
       <c r="R16" t="n">
-        <v>6994921</v>
+        <v>6994901</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,10 +2368,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121345126</v>
+        <v>121346453</v>
       </c>
       <c r="B17" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518549</v>
+        <v>518587</v>
       </c>
       <c r="R17" t="n">
-        <v>6994945</v>
+        <v>6994869</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,10 +2480,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121345407</v>
+        <v>121345182</v>
       </c>
       <c r="B18" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2516,14 +2516,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518425</v>
+        <v>518545</v>
       </c>
       <c r="R18" t="n">
-        <v>6994937</v>
+        <v>6994921</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 29455-2024 artfynd.xlsx
+++ b/artfynd/A 29455-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121345815</v>
+        <v>121345492</v>
       </c>
       <c r="B3" t="n">
-        <v>79685</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,37 +816,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518330</v>
+        <v>518419</v>
       </c>
       <c r="R3" t="n">
-        <v>6995067</v>
+        <v>6994943</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +912,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121345682</v>
+        <v>121345407</v>
       </c>
       <c r="B4" t="n">
         <v>78604</v>
@@ -948,17 +948,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518350</v>
+        <v>518425</v>
       </c>
       <c r="R4" t="n">
-        <v>6995000</v>
+        <v>6994937</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121345126</v>
+        <v>121345279</v>
       </c>
       <c r="B5" t="n">
         <v>78604</v>
@@ -1060,14 +1060,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518549</v>
+        <v>518470</v>
       </c>
       <c r="R5" t="n">
-        <v>6994945</v>
+        <v>6994910</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,7 +1136,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121345292</v>
+        <v>121345790</v>
       </c>
       <c r="B6" t="n">
         <v>78604</v>
@@ -1172,14 +1172,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518458</v>
+        <v>518340</v>
       </c>
       <c r="R6" t="n">
-        <v>6994899</v>
+        <v>6995031</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121345279</v>
+        <v>121345258</v>
       </c>
       <c r="B7" t="n">
-        <v>78604</v>
+        <v>90710</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,21 +1264,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518470</v>
+        <v>518502</v>
       </c>
       <c r="R7" t="n">
-        <v>6994910</v>
+        <v>6994901</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1472,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121345795</v>
+        <v>121345126</v>
       </c>
       <c r="B9" t="n">
-        <v>79685</v>
+        <v>78604</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1488,34 +1488,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518338</v>
+        <v>518549</v>
       </c>
       <c r="R9" t="n">
-        <v>6995040</v>
+        <v>6994945</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,7 +1584,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121345245</v>
+        <v>121345841</v>
       </c>
       <c r="B10" t="n">
         <v>78604</v>
@@ -1620,17 +1620,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518511</v>
+        <v>518331</v>
       </c>
       <c r="R10" t="n">
-        <v>6994904</v>
+        <v>6995058</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,7 +1696,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121345841</v>
+        <v>121345245</v>
       </c>
       <c r="B11" t="n">
         <v>78604</v>
@@ -1732,17 +1732,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518331</v>
+        <v>518511</v>
       </c>
       <c r="R11" t="n">
-        <v>6995058</v>
+        <v>6994904</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,7 +1808,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121345492</v>
+        <v>121345182</v>
       </c>
       <c r="B12" t="n">
         <v>78604</v>
@@ -1844,17 +1844,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518419</v>
+        <v>518545</v>
       </c>
       <c r="R12" t="n">
-        <v>6994943</v>
+        <v>6994921</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,10 +1920,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121345407</v>
+        <v>121345815</v>
       </c>
       <c r="B13" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1936,34 +1936,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518425</v>
+        <v>518330</v>
       </c>
       <c r="R13" t="n">
-        <v>6994937</v>
+        <v>6995067</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,10 +2032,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121345790</v>
+        <v>121345795</v>
       </c>
       <c r="B14" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2048,21 +2048,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518340</v>
+        <v>518338</v>
       </c>
       <c r="R14" t="n">
-        <v>6995031</v>
+        <v>6995040</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,7 +2144,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121346471</v>
+        <v>121346453</v>
       </c>
       <c r="B15" t="n">
         <v>78604</v>
@@ -2180,14 +2180,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518606</v>
+        <v>518587</v>
       </c>
       <c r="R15" t="n">
-        <v>6994830</v>
+        <v>6994869</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,10 +2256,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121345258</v>
+        <v>121345682</v>
       </c>
       <c r="B16" t="n">
-        <v>90709</v>
+        <v>78604</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2272,37 +2272,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518502</v>
+        <v>518350</v>
       </c>
       <c r="R16" t="n">
-        <v>6994901</v>
+        <v>6995000</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,7 +2368,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121346453</v>
+        <v>121345292</v>
       </c>
       <c r="B17" t="n">
         <v>78604</v>
@@ -2404,14 +2404,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518587</v>
+        <v>518458</v>
       </c>
       <c r="R17" t="n">
-        <v>6994869</v>
+        <v>6994899</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,7 +2480,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121345182</v>
+        <v>121346471</v>
       </c>
       <c r="B18" t="n">
         <v>78604</v>
@@ -2516,14 +2516,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518545</v>
+        <v>518606</v>
       </c>
       <c r="R18" t="n">
-        <v>6994921</v>
+        <v>6994830</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 29455-2024 artfynd.xlsx
+++ b/artfynd/A 29455-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121345492</v>
+        <v>121345126</v>
       </c>
       <c r="B3" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518419</v>
+        <v>518549</v>
       </c>
       <c r="R3" t="n">
-        <v>6994943</v>
+        <v>6994945</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121345407</v>
+        <v>121346471</v>
       </c>
       <c r="B4" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,14 +948,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518425</v>
+        <v>518606</v>
       </c>
       <c r="R4" t="n">
-        <v>6994937</v>
+        <v>6994830</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121345279</v>
+        <v>121346453</v>
       </c>
       <c r="B5" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,14 +1060,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518470</v>
+        <v>518587</v>
       </c>
       <c r="R5" t="n">
-        <v>6994910</v>
+        <v>6994869</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121345790</v>
+        <v>121345798</v>
       </c>
       <c r="B6" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518340</v>
+        <v>518332</v>
       </c>
       <c r="R6" t="n">
-        <v>6995031</v>
+        <v>6995045</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121345258</v>
+        <v>121345795</v>
       </c>
       <c r="B7" t="n">
-        <v>90710</v>
+        <v>79688</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,34 +1264,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518502</v>
+        <v>518338</v>
       </c>
       <c r="R7" t="n">
-        <v>6994901</v>
+        <v>6995040</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121345798</v>
+        <v>121345407</v>
       </c>
       <c r="B8" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1396,17 +1396,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518332</v>
+        <v>518425</v>
       </c>
       <c r="R8" t="n">
-        <v>6995045</v>
+        <v>6994937</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121345126</v>
+        <v>121345682</v>
       </c>
       <c r="B9" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1508,17 +1508,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518549</v>
+        <v>518350</v>
       </c>
       <c r="R9" t="n">
-        <v>6994945</v>
+        <v>6995000</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121345841</v>
+        <v>121345258</v>
       </c>
       <c r="B10" t="n">
-        <v>78604</v>
+        <v>90713</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,37 +1600,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518331</v>
+        <v>518502</v>
       </c>
       <c r="R10" t="n">
-        <v>6995058</v>
+        <v>6994901</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121345245</v>
+        <v>121345841</v>
       </c>
       <c r="B11" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,17 +1732,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518511</v>
+        <v>518331</v>
       </c>
       <c r="R11" t="n">
-        <v>6994904</v>
+        <v>6995058</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,7 +1811,7 @@
         <v>121345182</v>
       </c>
       <c r="B12" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1920,10 +1920,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121345815</v>
+        <v>121345790</v>
       </c>
       <c r="B13" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1936,21 +1936,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518330</v>
+        <v>518340</v>
       </c>
       <c r="R13" t="n">
-        <v>6995067</v>
+        <v>6995031</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,10 +2032,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121345795</v>
+        <v>121345245</v>
       </c>
       <c r="B14" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2048,37 +2048,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518338</v>
+        <v>518511</v>
       </c>
       <c r="R14" t="n">
-        <v>6995040</v>
+        <v>6994904</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,10 +2144,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121346453</v>
+        <v>121345815</v>
       </c>
       <c r="B15" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2160,34 +2160,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518587</v>
+        <v>518330</v>
       </c>
       <c r="R15" t="n">
-        <v>6994869</v>
+        <v>6995067</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,10 +2256,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121345682</v>
+        <v>121345279</v>
       </c>
       <c r="B16" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2292,17 +2292,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518350</v>
+        <v>518470</v>
       </c>
       <c r="R16" t="n">
-        <v>6995000</v>
+        <v>6994910</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,7 +2371,7 @@
         <v>121345292</v>
       </c>
       <c r="B17" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121346471</v>
+        <v>121345492</v>
       </c>
       <c r="B18" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2516,17 +2516,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518606</v>
+        <v>518419</v>
       </c>
       <c r="R18" t="n">
-        <v>6994830</v>
+        <v>6994943</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 29455-2024 artfynd.xlsx
+++ b/artfynd/A 29455-2024 artfynd.xlsx
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121345126</v>
+        <v>121345279</v>
       </c>
       <c r="B3" t="n">
         <v>78607</v>
@@ -836,14 +836,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518549</v>
+        <v>518470</v>
       </c>
       <c r="R3" t="n">
-        <v>6994945</v>
+        <v>6994910</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121346471</v>
+        <v>121345815</v>
       </c>
       <c r="B4" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,34 +928,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518606</v>
+        <v>518330</v>
       </c>
       <c r="R4" t="n">
-        <v>6994830</v>
+        <v>6995067</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121346453</v>
+        <v>121345795</v>
       </c>
       <c r="B5" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,34 +1040,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518587</v>
+        <v>518338</v>
       </c>
       <c r="R5" t="n">
-        <v>6994869</v>
+        <v>6995040</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121345795</v>
+        <v>121345492</v>
       </c>
       <c r="B7" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,37 +1264,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518338</v>
+        <v>518419</v>
       </c>
       <c r="R7" t="n">
-        <v>6995040</v>
+        <v>6994943</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121345407</v>
+        <v>121345258</v>
       </c>
       <c r="B8" t="n">
-        <v>78607</v>
+        <v>90713</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,21 +1376,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1400,10 +1400,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518425</v>
+        <v>518502</v>
       </c>
       <c r="R8" t="n">
-        <v>6994937</v>
+        <v>6994901</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121345258</v>
+        <v>121346453</v>
       </c>
       <c r="B10" t="n">
-        <v>90713</v>
+        <v>78607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,34 +1600,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518502</v>
+        <v>518587</v>
       </c>
       <c r="R10" t="n">
-        <v>6994901</v>
+        <v>6994869</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,7 +1696,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121345841</v>
+        <v>121345292</v>
       </c>
       <c r="B11" t="n">
         <v>78607</v>
@@ -1732,17 +1732,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518331</v>
+        <v>518458</v>
       </c>
       <c r="R11" t="n">
-        <v>6995058</v>
+        <v>6994899</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1920,7 +1920,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121345790</v>
+        <v>121345841</v>
       </c>
       <c r="B13" t="n">
         <v>78607</v>
@@ -1960,13 +1960,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518340</v>
+        <v>518331</v>
       </c>
       <c r="R13" t="n">
-        <v>6995031</v>
+        <v>6995058</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,7 +2032,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121345245</v>
+        <v>121346471</v>
       </c>
       <c r="B14" t="n">
         <v>78607</v>
@@ -2068,17 +2068,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518511</v>
+        <v>518606</v>
       </c>
       <c r="R14" t="n">
-        <v>6994904</v>
+        <v>6994830</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,10 +2144,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121345815</v>
+        <v>121345245</v>
       </c>
       <c r="B15" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2160,37 +2160,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518330</v>
+        <v>518511</v>
       </c>
       <c r="R15" t="n">
-        <v>6995067</v>
+        <v>6994904</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,7 +2256,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121345279</v>
+        <v>121345407</v>
       </c>
       <c r="B16" t="n">
         <v>78607</v>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518470</v>
+        <v>518425</v>
       </c>
       <c r="R16" t="n">
-        <v>6994910</v>
+        <v>6994937</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,7 +2368,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121345292</v>
+        <v>121345126</v>
       </c>
       <c r="B17" t="n">
         <v>78607</v>
@@ -2404,14 +2404,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518458</v>
+        <v>518549</v>
       </c>
       <c r="R17" t="n">
-        <v>6994899</v>
+        <v>6994945</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,7 +2480,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121345492</v>
+        <v>121345790</v>
       </c>
       <c r="B18" t="n">
         <v>78607</v>
@@ -2516,17 +2516,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518419</v>
+        <v>518340</v>
       </c>
       <c r="R18" t="n">
-        <v>6994943</v>
+        <v>6995031</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 29455-2024 artfynd.xlsx
+++ b/artfynd/A 29455-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121345279</v>
+        <v>121345682</v>
       </c>
       <c r="B3" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518470</v>
+        <v>518350</v>
       </c>
       <c r="R3" t="n">
-        <v>6994910</v>
+        <v>6995000</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121345815</v>
+        <v>121346453</v>
       </c>
       <c r="B4" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,34 +928,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518330</v>
+        <v>518587</v>
       </c>
       <c r="R4" t="n">
-        <v>6995067</v>
+        <v>6994869</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121345795</v>
+        <v>121345279</v>
       </c>
       <c r="B5" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,34 +1040,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518338</v>
+        <v>518470</v>
       </c>
       <c r="R5" t="n">
-        <v>6995040</v>
+        <v>6994910</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121345798</v>
+        <v>121345492</v>
       </c>
       <c r="B6" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,14 +1172,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518332</v>
+        <v>518419</v>
       </c>
       <c r="R6" t="n">
-        <v>6995045</v>
+        <v>6994943</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121345492</v>
+        <v>121345841</v>
       </c>
       <c r="B7" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,17 +1284,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518419</v>
+        <v>518331</v>
       </c>
       <c r="R7" t="n">
-        <v>6994943</v>
+        <v>6995058</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121345258</v>
+        <v>121345795</v>
       </c>
       <c r="B8" t="n">
-        <v>90713</v>
+        <v>79689</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,34 +1376,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518502</v>
+        <v>518338</v>
       </c>
       <c r="R8" t="n">
-        <v>6994901</v>
+        <v>6995040</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121345682</v>
+        <v>121345126</v>
       </c>
       <c r="B9" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1508,17 +1508,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518350</v>
+        <v>518549</v>
       </c>
       <c r="R9" t="n">
-        <v>6995000</v>
+        <v>6994945</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121346453</v>
+        <v>121345815</v>
       </c>
       <c r="B10" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,34 +1600,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518587</v>
+        <v>518330</v>
       </c>
       <c r="R10" t="n">
-        <v>6994869</v>
+        <v>6995067</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121345292</v>
+        <v>121345258</v>
       </c>
       <c r="B11" t="n">
-        <v>78607</v>
+        <v>90719</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,21 +1712,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518458</v>
+        <v>518502</v>
       </c>
       <c r="R11" t="n">
-        <v>6994899</v>
+        <v>6994901</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121345182</v>
+        <v>121345292</v>
       </c>
       <c r="B12" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1844,14 +1844,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518545</v>
+        <v>518458</v>
       </c>
       <c r="R12" t="n">
-        <v>6994921</v>
+        <v>6994899</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,10 +1920,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121345841</v>
+        <v>121345245</v>
       </c>
       <c r="B13" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,17 +1956,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518331</v>
+        <v>518511</v>
       </c>
       <c r="R13" t="n">
-        <v>6995058</v>
+        <v>6994904</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,10 +2032,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121346471</v>
+        <v>121345790</v>
       </c>
       <c r="B14" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,14 +2068,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518606</v>
+        <v>518340</v>
       </c>
       <c r="R14" t="n">
-        <v>6994830</v>
+        <v>6995031</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,10 +2144,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121345245</v>
+        <v>121346471</v>
       </c>
       <c r="B15" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2180,17 +2180,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518511</v>
+        <v>518606</v>
       </c>
       <c r="R15" t="n">
-        <v>6994904</v>
+        <v>6994830</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2259,7 +2259,7 @@
         <v>121345407</v>
       </c>
       <c r="B16" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121345126</v>
+        <v>121345182</v>
       </c>
       <c r="B17" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518549</v>
+        <v>518545</v>
       </c>
       <c r="R17" t="n">
-        <v>6994945</v>
+        <v>6994921</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,10 +2480,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121345790</v>
+        <v>121345798</v>
       </c>
       <c r="B18" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2520,13 +2520,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518340</v>
+        <v>518332</v>
       </c>
       <c r="R18" t="n">
-        <v>6995031</v>
+        <v>6995045</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 29455-2024 artfynd.xlsx
+++ b/artfynd/A 29455-2024 artfynd.xlsx
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121345815</v>
+        <v>121345258</v>
       </c>
       <c r="B10" t="n">
-        <v>79689</v>
+        <v>90719</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,34 +1600,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518330</v>
+        <v>518502</v>
       </c>
       <c r="R10" t="n">
-        <v>6995067</v>
+        <v>6994901</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121345258</v>
+        <v>121345815</v>
       </c>
       <c r="B11" t="n">
-        <v>90719</v>
+        <v>79689</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,34 +1712,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518502</v>
+        <v>518330</v>
       </c>
       <c r="R11" t="n">
-        <v>6994901</v>
+        <v>6995067</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 29455-2024 artfynd.xlsx
+++ b/artfynd/A 29455-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121345682</v>
+        <v>121345790</v>
       </c>
       <c r="B3" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -840,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518350</v>
+        <v>518340</v>
       </c>
       <c r="R3" t="n">
-        <v>6995000</v>
+        <v>6995031</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121346453</v>
+        <v>121345126</v>
       </c>
       <c r="B4" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518587</v>
+        <v>518549</v>
       </c>
       <c r="R4" t="n">
-        <v>6994869</v>
+        <v>6994945</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121345279</v>
+        <v>121345682</v>
       </c>
       <c r="B5" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,17 +1060,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518470</v>
+        <v>518350</v>
       </c>
       <c r="R5" t="n">
-        <v>6994910</v>
+        <v>6995000</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121345492</v>
+        <v>121345182</v>
       </c>
       <c r="B6" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,17 +1172,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518419</v>
+        <v>518545</v>
       </c>
       <c r="R6" t="n">
-        <v>6994943</v>
+        <v>6994921</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121345841</v>
+        <v>121345292</v>
       </c>
       <c r="B7" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,17 +1284,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518331</v>
+        <v>518458</v>
       </c>
       <c r="R7" t="n">
-        <v>6995058</v>
+        <v>6994899</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121345795</v>
+        <v>121346453</v>
       </c>
       <c r="B8" t="n">
-        <v>79689</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,34 +1376,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518338</v>
+        <v>518587</v>
       </c>
       <c r="R8" t="n">
-        <v>6995040</v>
+        <v>6994869</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121345126</v>
+        <v>121345258</v>
       </c>
       <c r="B9" t="n">
-        <v>78608</v>
+        <v>90720</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1488,34 +1488,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518549</v>
+        <v>518502</v>
       </c>
       <c r="R9" t="n">
-        <v>6994945</v>
+        <v>6994901</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121345258</v>
+        <v>121345841</v>
       </c>
       <c r="B10" t="n">
-        <v>90719</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,37 +1600,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518502</v>
+        <v>518331</v>
       </c>
       <c r="R10" t="n">
-        <v>6994901</v>
+        <v>6995058</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121345815</v>
+        <v>121345795</v>
       </c>
       <c r="B11" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518330</v>
+        <v>518338</v>
       </c>
       <c r="R11" t="n">
-        <v>6995067</v>
+        <v>6995040</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121345292</v>
+        <v>121345492</v>
       </c>
       <c r="B12" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1848,13 +1848,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518458</v>
+        <v>518419</v>
       </c>
       <c r="R12" t="n">
-        <v>6994899</v>
+        <v>6994943</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,10 +1920,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121345245</v>
+        <v>121345279</v>
       </c>
       <c r="B13" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1960,13 +1960,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518511</v>
+        <v>518470</v>
       </c>
       <c r="R13" t="n">
-        <v>6994904</v>
+        <v>6994910</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,10 +2032,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121345790</v>
+        <v>121345798</v>
       </c>
       <c r="B14" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518340</v>
+        <v>518332</v>
       </c>
       <c r="R14" t="n">
-        <v>6995031</v>
+        <v>6995045</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,10 +2144,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121346471</v>
+        <v>121345407</v>
       </c>
       <c r="B15" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2180,14 +2180,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518606</v>
+        <v>518425</v>
       </c>
       <c r="R15" t="n">
-        <v>6994830</v>
+        <v>6994937</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,10 +2256,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121345407</v>
+        <v>121346471</v>
       </c>
       <c r="B16" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2292,14 +2292,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518425</v>
+        <v>518606</v>
       </c>
       <c r="R16" t="n">
-        <v>6994937</v>
+        <v>6994830</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,10 +2368,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121345182</v>
+        <v>121345815</v>
       </c>
       <c r="B17" t="n">
-        <v>78608</v>
+        <v>79690</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2384,34 +2384,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518545</v>
+        <v>518330</v>
       </c>
       <c r="R17" t="n">
-        <v>6994921</v>
+        <v>6995067</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,10 +2480,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121345798</v>
+        <v>121345245</v>
       </c>
       <c r="B18" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2516,14 +2516,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518332</v>
+        <v>518511</v>
       </c>
       <c r="R18" t="n">
-        <v>6995045</v>
+        <v>6994904</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 29455-2024 artfynd.xlsx
+++ b/artfynd/A 29455-2024 artfynd.xlsx
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121345790</v>
+        <v>121345682</v>
       </c>
       <c r="B3" t="n">
         <v>78609</v>
@@ -840,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518340</v>
+        <v>518350</v>
       </c>
       <c r="R3" t="n">
-        <v>6995031</v>
+        <v>6995000</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +912,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121345126</v>
+        <v>121345407</v>
       </c>
       <c r="B4" t="n">
         <v>78609</v>
@@ -948,14 +948,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518549</v>
+        <v>518425</v>
       </c>
       <c r="R4" t="n">
-        <v>6994945</v>
+        <v>6994937</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121345682</v>
+        <v>121345841</v>
       </c>
       <c r="B5" t="n">
         <v>78609</v>
@@ -1064,13 +1064,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518350</v>
+        <v>518331</v>
       </c>
       <c r="R5" t="n">
-        <v>6995000</v>
+        <v>6995058</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,7 +1136,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121345182</v>
+        <v>121345279</v>
       </c>
       <c r="B6" t="n">
         <v>78609</v>
@@ -1172,14 +1172,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518545</v>
+        <v>518470</v>
       </c>
       <c r="R6" t="n">
-        <v>6994921</v>
+        <v>6994910</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1360,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121346453</v>
+        <v>121345795</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,34 +1376,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518587</v>
+        <v>518338</v>
       </c>
       <c r="R8" t="n">
-        <v>6994869</v>
+        <v>6995040</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1584,7 +1584,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121345841</v>
+        <v>121345790</v>
       </c>
       <c r="B10" t="n">
         <v>78609</v>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518331</v>
+        <v>518340</v>
       </c>
       <c r="R10" t="n">
-        <v>6995058</v>
+        <v>6995031</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121345795</v>
+        <v>121346471</v>
       </c>
       <c r="B11" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,34 +1712,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518338</v>
+        <v>518606</v>
       </c>
       <c r="R11" t="n">
-        <v>6995040</v>
+        <v>6994830</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,7 +1808,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121345492</v>
+        <v>121345798</v>
       </c>
       <c r="B12" t="n">
         <v>78609</v>
@@ -1844,14 +1844,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518419</v>
+        <v>518332</v>
       </c>
       <c r="R12" t="n">
-        <v>6994943</v>
+        <v>6995045</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,10 +1920,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121345279</v>
+        <v>121345815</v>
       </c>
       <c r="B13" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1936,34 +1936,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518470</v>
+        <v>518330</v>
       </c>
       <c r="R13" t="n">
-        <v>6994910</v>
+        <v>6995067</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,7 +2032,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121345798</v>
+        <v>121345492</v>
       </c>
       <c r="B14" t="n">
         <v>78609</v>
@@ -2068,14 +2068,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518332</v>
+        <v>518419</v>
       </c>
       <c r="R14" t="n">
-        <v>6995045</v>
+        <v>6994943</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,7 +2144,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121345407</v>
+        <v>121346453</v>
       </c>
       <c r="B15" t="n">
         <v>78609</v>
@@ -2180,14 +2180,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518425</v>
+        <v>518587</v>
       </c>
       <c r="R15" t="n">
-        <v>6994937</v>
+        <v>6994869</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,7 +2256,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121346471</v>
+        <v>121345126</v>
       </c>
       <c r="B16" t="n">
         <v>78609</v>
@@ -2292,14 +2292,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518606</v>
+        <v>518549</v>
       </c>
       <c r="R16" t="n">
-        <v>6994830</v>
+        <v>6994945</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,10 +2368,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121345815</v>
+        <v>121345245</v>
       </c>
       <c r="B17" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2384,37 +2384,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518330</v>
+        <v>518511</v>
       </c>
       <c r="R17" t="n">
-        <v>6995067</v>
+        <v>6994904</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,7 +2480,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121345245</v>
+        <v>121345182</v>
       </c>
       <c r="B18" t="n">
         <v>78609</v>
@@ -2516,17 +2516,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518511</v>
+        <v>518545</v>
       </c>
       <c r="R18" t="n">
-        <v>6994904</v>
+        <v>6994921</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 29455-2024 artfynd.xlsx
+++ b/artfynd/A 29455-2024 artfynd.xlsx
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121345682</v>
+        <v>121345841</v>
       </c>
       <c r="B3" t="n">
         <v>78609</v>
@@ -840,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518350</v>
+        <v>518331</v>
       </c>
       <c r="R3" t="n">
-        <v>6995000</v>
+        <v>6995058</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +912,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121345407</v>
+        <v>121345292</v>
       </c>
       <c r="B4" t="n">
         <v>78609</v>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518425</v>
+        <v>518458</v>
       </c>
       <c r="R4" t="n">
-        <v>6994937</v>
+        <v>6994899</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121345841</v>
+        <v>121346453</v>
       </c>
       <c r="B5" t="n">
         <v>78609</v>
@@ -1060,17 +1060,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518331</v>
+        <v>518587</v>
       </c>
       <c r="R5" t="n">
-        <v>6995058</v>
+        <v>6994869</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121345279</v>
+        <v>121345258</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,21 +1152,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518470</v>
+        <v>518502</v>
       </c>
       <c r="R6" t="n">
-        <v>6994910</v>
+        <v>6994901</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121345292</v>
+        <v>121345795</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,34 +1264,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518458</v>
+        <v>518338</v>
       </c>
       <c r="R7" t="n">
-        <v>6994899</v>
+        <v>6995040</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121345795</v>
+        <v>121345126</v>
       </c>
       <c r="B8" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,34 +1376,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518338</v>
+        <v>518549</v>
       </c>
       <c r="R8" t="n">
-        <v>6995040</v>
+        <v>6994945</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121345258</v>
+        <v>121345407</v>
       </c>
       <c r="B9" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1488,21 +1488,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518502</v>
+        <v>518425</v>
       </c>
       <c r="R9" t="n">
-        <v>6994901</v>
+        <v>6994937</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,7 +1584,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121345790</v>
+        <v>121345279</v>
       </c>
       <c r="B10" t="n">
         <v>78609</v>
@@ -1620,14 +1620,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518340</v>
+        <v>518470</v>
       </c>
       <c r="R10" t="n">
-        <v>6995031</v>
+        <v>6994910</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,7 +1696,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121346471</v>
+        <v>121345182</v>
       </c>
       <c r="B11" t="n">
         <v>78609</v>
@@ -1732,14 +1732,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518606</v>
+        <v>518545</v>
       </c>
       <c r="R11" t="n">
-        <v>6994830</v>
+        <v>6994921</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,7 +1808,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121345798</v>
+        <v>121345682</v>
       </c>
       <c r="B12" t="n">
         <v>78609</v>
@@ -1848,10 +1848,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518332</v>
+        <v>518350</v>
       </c>
       <c r="R12" t="n">
-        <v>6995045</v>
+        <v>6995000</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2032,7 +2032,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121345492</v>
+        <v>121345790</v>
       </c>
       <c r="B14" t="n">
         <v>78609</v>
@@ -2068,17 +2068,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518419</v>
+        <v>518340</v>
       </c>
       <c r="R14" t="n">
-        <v>6994943</v>
+        <v>6995031</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,7 +2144,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121346453</v>
+        <v>121345245</v>
       </c>
       <c r="B15" t="n">
         <v>78609</v>
@@ -2180,17 +2180,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518587</v>
+        <v>518511</v>
       </c>
       <c r="R15" t="n">
-        <v>6994869</v>
+        <v>6994904</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,7 +2256,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121345126</v>
+        <v>121346471</v>
       </c>
       <c r="B16" t="n">
         <v>78609</v>
@@ -2292,14 +2292,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518549</v>
+        <v>518606</v>
       </c>
       <c r="R16" t="n">
-        <v>6994945</v>
+        <v>6994830</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,7 +2368,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121345245</v>
+        <v>121345798</v>
       </c>
       <c r="B17" t="n">
         <v>78609</v>
@@ -2404,14 +2404,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518511</v>
+        <v>518332</v>
       </c>
       <c r="R17" t="n">
-        <v>6994904</v>
+        <v>6995045</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,7 +2480,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121345182</v>
+        <v>121345492</v>
       </c>
       <c r="B18" t="n">
         <v>78609</v>
@@ -2516,17 +2516,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518545</v>
+        <v>518419</v>
       </c>
       <c r="R18" t="n">
-        <v>6994921</v>
+        <v>6994943</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 29455-2024 artfynd.xlsx
+++ b/artfynd/A 29455-2024 artfynd.xlsx
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121345841</v>
+        <v>121345245</v>
       </c>
       <c r="B3" t="n">
         <v>78609</v>
@@ -836,17 +836,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518331</v>
+        <v>518511</v>
       </c>
       <c r="R3" t="n">
-        <v>6995058</v>
+        <v>6994904</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +912,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121345292</v>
+        <v>121346471</v>
       </c>
       <c r="B4" t="n">
         <v>78609</v>
@@ -948,14 +948,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518458</v>
+        <v>518606</v>
       </c>
       <c r="R4" t="n">
-        <v>6994899</v>
+        <v>6994830</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121346453</v>
+        <v>121345682</v>
       </c>
       <c r="B5" t="n">
         <v>78609</v>
@@ -1060,17 +1060,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518587</v>
+        <v>518350</v>
       </c>
       <c r="R5" t="n">
-        <v>6994869</v>
+        <v>6995000</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121345258</v>
+        <v>121345126</v>
       </c>
       <c r="B6" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,34 +1152,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518502</v>
+        <v>518549</v>
       </c>
       <c r="R6" t="n">
-        <v>6994901</v>
+        <v>6994945</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,7 +1248,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121345795</v>
+        <v>121345815</v>
       </c>
       <c r="B7" t="n">
         <v>79690</v>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518338</v>
+        <v>518330</v>
       </c>
       <c r="R7" t="n">
-        <v>6995040</v>
+        <v>6995067</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,7 +1360,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121345126</v>
+        <v>121345292</v>
       </c>
       <c r="B8" t="n">
         <v>78609</v>
@@ -1396,14 +1396,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518549</v>
+        <v>518458</v>
       </c>
       <c r="R8" t="n">
-        <v>6994945</v>
+        <v>6994899</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,7 +1472,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121345407</v>
+        <v>121346453</v>
       </c>
       <c r="B9" t="n">
         <v>78609</v>
@@ -1508,14 +1508,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518425</v>
+        <v>518587</v>
       </c>
       <c r="R9" t="n">
-        <v>6994937</v>
+        <v>6994869</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,7 +1584,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121345279</v>
+        <v>121345790</v>
       </c>
       <c r="B10" t="n">
         <v>78609</v>
@@ -1620,14 +1620,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518470</v>
+        <v>518340</v>
       </c>
       <c r="R10" t="n">
-        <v>6994910</v>
+        <v>6995031</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121345182</v>
+        <v>121345258</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,34 +1712,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518545</v>
+        <v>518502</v>
       </c>
       <c r="R11" t="n">
-        <v>6994921</v>
+        <v>6994901</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121345682</v>
+        <v>121345795</v>
       </c>
       <c r="B12" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1824,21 +1824,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1848,13 +1848,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518350</v>
+        <v>518338</v>
       </c>
       <c r="R12" t="n">
-        <v>6995000</v>
+        <v>6995040</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,10 +1920,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121345815</v>
+        <v>121345182</v>
       </c>
       <c r="B13" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1936,34 +1936,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518330</v>
+        <v>518545</v>
       </c>
       <c r="R13" t="n">
-        <v>6995067</v>
+        <v>6994921</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,7 +2032,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121345790</v>
+        <v>121345279</v>
       </c>
       <c r="B14" t="n">
         <v>78609</v>
@@ -2068,14 +2068,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518340</v>
+        <v>518470</v>
       </c>
       <c r="R14" t="n">
-        <v>6995031</v>
+        <v>6994910</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,7 +2144,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121345245</v>
+        <v>121345798</v>
       </c>
       <c r="B15" t="n">
         <v>78609</v>
@@ -2180,14 +2180,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518511</v>
+        <v>518332</v>
       </c>
       <c r="R15" t="n">
-        <v>6994904</v>
+        <v>6995045</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,7 +2256,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121346471</v>
+        <v>121345841</v>
       </c>
       <c r="B16" t="n">
         <v>78609</v>
@@ -2292,17 +2292,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518606</v>
+        <v>518331</v>
       </c>
       <c r="R16" t="n">
-        <v>6994830</v>
+        <v>6995058</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,7 +2368,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121345798</v>
+        <v>121345407</v>
       </c>
       <c r="B17" t="n">
         <v>78609</v>
@@ -2404,17 +2404,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518332</v>
+        <v>518425</v>
       </c>
       <c r="R17" t="n">
-        <v>6995045</v>
+        <v>6994937</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 29455-2024 artfynd.xlsx
+++ b/artfynd/A 29455-2024 artfynd.xlsx
@@ -1808,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121345795</v>
+        <v>121345182</v>
       </c>
       <c r="B12" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1824,34 +1824,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518338</v>
+        <v>518545</v>
       </c>
       <c r="R12" t="n">
-        <v>6995040</v>
+        <v>6994921</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,10 +1920,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121345182</v>
+        <v>121345795</v>
       </c>
       <c r="B13" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1936,34 +1936,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518545</v>
+        <v>518338</v>
       </c>
       <c r="R13" t="n">
-        <v>6994921</v>
+        <v>6995040</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 29455-2024 artfynd.xlsx
+++ b/artfynd/A 29455-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121345245</v>
+        <v>121346471</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518511</v>
+        <v>518606</v>
       </c>
       <c r="R3" t="n">
-        <v>6994904</v>
+        <v>6994830</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121346471</v>
+        <v>121345492</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,17 +948,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518606</v>
+        <v>518419</v>
       </c>
       <c r="R4" t="n">
-        <v>6994830</v>
+        <v>6994943</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121345682</v>
+        <v>121345126</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,17 +1060,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518350</v>
+        <v>518549</v>
       </c>
       <c r="R5" t="n">
-        <v>6995000</v>
+        <v>6994945</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121345126</v>
+        <v>121345245</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,17 +1172,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518549</v>
+        <v>518511</v>
       </c>
       <c r="R6" t="n">
-        <v>6994945</v>
+        <v>6994904</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,7 +1251,7 @@
         <v>121345815</v>
       </c>
       <c r="B7" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121345292</v>
+        <v>121345182</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1396,14 +1396,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518458</v>
+        <v>518545</v>
       </c>
       <c r="R8" t="n">
-        <v>6994899</v>
+        <v>6994921</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121346453</v>
+        <v>121345258</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>90728</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1488,34 +1488,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518587</v>
+        <v>518502</v>
       </c>
       <c r="R9" t="n">
-        <v>6994869</v>
+        <v>6994901</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121345790</v>
+        <v>121345682</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518340</v>
+        <v>518350</v>
       </c>
       <c r="R10" t="n">
-        <v>6995031</v>
+        <v>6995000</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121345258</v>
+        <v>121345292</v>
       </c>
       <c r="B11" t="n">
-        <v>90720</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,21 +1712,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518502</v>
+        <v>518458</v>
       </c>
       <c r="R11" t="n">
-        <v>6994901</v>
+        <v>6994899</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121345182</v>
+        <v>121345841</v>
       </c>
       <c r="B12" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1844,17 +1844,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518545</v>
+        <v>518331</v>
       </c>
       <c r="R12" t="n">
-        <v>6994921</v>
+        <v>6995058</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,10 +1920,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121345795</v>
+        <v>121345407</v>
       </c>
       <c r="B13" t="n">
-        <v>79690</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1936,34 +1936,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518338</v>
+        <v>518425</v>
       </c>
       <c r="R13" t="n">
-        <v>6995040</v>
+        <v>6994937</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,10 +2032,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121345279</v>
+        <v>121345795</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>79697</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2048,34 +2048,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518470</v>
+        <v>518338</v>
       </c>
       <c r="R14" t="n">
-        <v>6994910</v>
+        <v>6995040</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,10 +2144,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121345798</v>
+        <v>121345279</v>
       </c>
       <c r="B15" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2180,17 +2180,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518332</v>
+        <v>518470</v>
       </c>
       <c r="R15" t="n">
-        <v>6995045</v>
+        <v>6994910</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,10 +2256,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121345841</v>
+        <v>121345798</v>
       </c>
       <c r="B16" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2296,13 +2296,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518331</v>
+        <v>518332</v>
       </c>
       <c r="R16" t="n">
-        <v>6995058</v>
+        <v>6995045</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,10 +2368,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121345407</v>
+        <v>121345790</v>
       </c>
       <c r="B17" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2404,14 +2404,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518425</v>
+        <v>518340</v>
       </c>
       <c r="R17" t="n">
-        <v>6994937</v>
+        <v>6995031</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,10 +2480,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121345492</v>
+        <v>121346453</v>
       </c>
       <c r="B18" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2516,17 +2516,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518419</v>
+        <v>518587</v>
       </c>
       <c r="R18" t="n">
-        <v>6994943</v>
+        <v>6994869</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 29455-2024 artfynd.xlsx
+++ b/artfynd/A 29455-2024 artfynd.xlsx
@@ -1472,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121345258</v>
+        <v>121345682</v>
       </c>
       <c r="B9" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1488,37 +1488,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518502</v>
+        <v>518350</v>
       </c>
       <c r="R9" t="n">
-        <v>6994901</v>
+        <v>6995000</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121345682</v>
+        <v>121345258</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,37 +1600,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518350</v>
+        <v>518502</v>
       </c>
       <c r="R10" t="n">
-        <v>6995000</v>
+        <v>6994901</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 29455-2024 artfynd.xlsx
+++ b/artfynd/A 29455-2024 artfynd.xlsx
@@ -1696,7 +1696,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121345292</v>
+        <v>121345841</v>
       </c>
       <c r="B11" t="n">
         <v>78616</v>
@@ -1732,17 +1732,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518458</v>
+        <v>518331</v>
       </c>
       <c r="R11" t="n">
-        <v>6994899</v>
+        <v>6995058</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,7 +1808,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121345841</v>
+        <v>121345292</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1844,17 +1844,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518331</v>
+        <v>518458</v>
       </c>
       <c r="R12" t="n">
-        <v>6995058</v>
+        <v>6994899</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 29455-2024 artfynd.xlsx
+++ b/artfynd/A 29455-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62023324</v>
+        <v>121345116</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Boggsjö, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518350.4733556812</v>
+        <v>518559</v>
       </c>
       <c r="R2" t="n">
-        <v>6994940.110071637</v>
+        <v>6994969</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +743,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-10-27</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-10-27</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,46 +767,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>1 substratenheter # sälg</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Jenny Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg, Sven Bengtsson</t>
+          <t>Jenny Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121345795</v>
+        <v>121345258</v>
       </c>
       <c r="B3" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518338</v>
+        <v>518502</v>
       </c>
       <c r="R3" t="n">
-        <v>6995040</v>
+        <v>6994901</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,19 +893,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121345407</v>
+        <v>121345122</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -948,14 +924,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518425</v>
+        <v>518552</v>
       </c>
       <c r="R4" t="n">
-        <v>6994937</v>
+        <v>6994973</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,50 +1000,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121345258</v>
+        <v>121345126</v>
       </c>
       <c r="B5" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518502</v>
+        <v>518549</v>
       </c>
       <c r="R5" t="n">
-        <v>6994901</v>
+        <v>6994945</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1070,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1080,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,19 +1107,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121345245</v>
+        <v>121345182</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1172,17 +1138,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518511</v>
+        <v>518545</v>
       </c>
       <c r="R6" t="n">
-        <v>6994904</v>
+        <v>6994921</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,7 +1177,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1187,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,19 +1214,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121346453</v>
+        <v>121345245</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1284,17 +1245,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518587</v>
+        <v>518511</v>
       </c>
       <c r="R7" t="n">
-        <v>6994869</v>
+        <v>6994904</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,7 +1284,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1294,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,19 +1321,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121345126</v>
+        <v>121345279</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1396,14 +1352,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518549</v>
+        <v>518470</v>
       </c>
       <c r="R8" t="n">
-        <v>6994945</v>
+        <v>6994910</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,7 +1391,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1401,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,19 +1428,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121345279</v>
+        <v>121345292</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1512,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518470</v>
+        <v>518458</v>
       </c>
       <c r="R9" t="n">
-        <v>6994910</v>
+        <v>6994899</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1498,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1508,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,50 +1535,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121345815</v>
+        <v>121345407</v>
       </c>
       <c r="B10" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518330</v>
+        <v>518425</v>
       </c>
       <c r="R10" t="n">
-        <v>6995067</v>
+        <v>6994937</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,7 +1605,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1615,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,19 +1642,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121346471</v>
+        <v>121345492</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1732,17 +1673,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518606</v>
+        <v>518419</v>
       </c>
       <c r="R11" t="n">
-        <v>6994830</v>
+        <v>6994943</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,7 +1712,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1722,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,19 +1749,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121345841</v>
+        <v>121345682</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1848,13 +1784,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518331</v>
+        <v>518350</v>
       </c>
       <c r="R12" t="n">
-        <v>6995058</v>
+        <v>6995000</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,7 +1819,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1829,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,16 +1859,11 @@
         <v>121345790</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2032,19 +1963,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121345292</v>
+        <v>121345798</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2068,17 +1994,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518458</v>
+        <v>518332</v>
       </c>
       <c r="R14" t="n">
-        <v>6994899</v>
+        <v>6995045</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2107,7 +2033,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,7 +2043,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,19 +2070,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121345182</v>
+        <v>121345841</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2180,17 +2101,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518545</v>
+        <v>518331</v>
       </c>
       <c r="R15" t="n">
-        <v>6994921</v>
+        <v>6995058</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2219,7 +2140,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2229,7 +2150,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,19 +2177,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121345682</v>
+        <v>121345864</v>
       </c>
       <c r="B16" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2296,13 +2212,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518350</v>
+        <v>518346</v>
       </c>
       <c r="R16" t="n">
-        <v>6995000</v>
+        <v>6995075</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2331,7 +2247,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,7 +2257,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,19 +2284,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121345798</v>
+        <v>121346430</v>
       </c>
       <c r="B17" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2404,17 +2315,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518332</v>
+        <v>518614</v>
       </c>
       <c r="R17" t="n">
-        <v>6995045</v>
+        <v>6994902</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2443,7 +2354,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2453,7 +2364,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,19 +2391,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121345492</v>
+        <v>121346453</v>
       </c>
       <c r="B18" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2516,17 +2422,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gårdsfloberget, Gårdsfloberget, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518419</v>
+        <v>518587</v>
       </c>
       <c r="R18" t="n">
-        <v>6994943</v>
+        <v>6994869</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2555,7 +2461,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2565,7 +2471,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,6 +2495,437 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121346471</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lugnet, Lugnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>518606</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6994830</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>62023324</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Boggsjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>518350</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6994940</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2016-10-27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2016-10-27</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AN20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>1 substratenheter # sälg</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg, Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121345795</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Linderråken, Linderråken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>518338</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6995040</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121345815</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Linderråken, Linderråken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>518330</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6995067</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29455-2024 artfynd.xlsx
+++ b/artfynd/A 29455-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121345116</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121345258</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121345122</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121345126</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121345182</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121345245</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1425,6 +1460,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121345279</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1532,6 +1572,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121345292</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1639,6 +1684,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121345407</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1746,6 +1796,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121345492</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1853,6 +1908,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121345682</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1960,6 +2020,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121345790</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2067,6 +2132,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121345798</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2174,6 +2244,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121345841</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2281,6 +2356,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121345864</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2388,6 +2468,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121346430</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2495,6 +2580,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121346453</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2602,6 +2692,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121346471</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2712,6 +2807,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62023324</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2819,6 +2919,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121345795</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2926,8 +3031,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121345815</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>